--- a/source_data/Daddario Price List - March-2025.xlsx
+++ b/source_data/Daddario Price List - March-2025.xlsx
@@ -1,22 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://roscoguitars.sharepoint.com/sites/RoscoGuitars/Shared Documents/05. Suppliers &amp; Parts/Price Lists/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Claytron\RoscoAI\rosco_projects\rosco-custom-strings\source_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="214" documentId="8_{1C56A2BA-FDE5-452E-946D-CB04192CA1F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{258E13BF-FE00-48FA-862F-92D3B1CD7167}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D36E6E9E-642B-4E59-9299-BFEB71186C1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Calculator" sheetId="2" r:id="rId1"/>
-    <sheet name="XL STRINGS" sheetId="3" r:id="rId2"/>
-    <sheet name="XLB Bass" sheetId="4" r:id="rId3"/>
-    <sheet name="Export" sheetId="1" r:id="rId4"/>
+    <sheet name="Daddario Price List 2025" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5844" uniqueCount="4054">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5410" uniqueCount="4043">
   <si>
     <t>ProdCode</t>
   </si>
@@ -12165,50 +12162,16 @@
   </si>
   <si>
     <t>019954323578</t>
-  </si>
-  <si>
-    <t>String</t>
-  </si>
-  <si>
-    <t>Cost</t>
-  </si>
-  <si>
-    <t>Total</t>
-  </si>
-  <si>
-    <t>Size</t>
-  </si>
-  <si>
-    <t>STRING</t>
-  </si>
-  <si>
-    <t>PRICE</t>
-  </si>
-  <si>
-    <t>Markup</t>
-  </si>
-  <si>
-    <t>Bass</t>
-  </si>
-  <si>
-    <t>Guitar</t>
-  </si>
-  <si>
-    <t>Price</t>
-  </si>
-  <si>
-    <t>Profit</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="\$#,##0.00;\(\$#,##0.00\);\$#,##0.00"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <name val="Aptos Narrow"/>
@@ -12229,28 +12192,8 @@
       <name val="Aptos"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <name val="Aptos Narrow"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Aptos Narrow"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -12284,18 +12227,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="1" tint="0.34998626667073579"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -12370,12 +12301,10 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -12406,25 +12335,9 @@
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="3">
-    <cellStyle name="Currency" xfId="1" builtinId="4"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -12760,2230 +12673,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B21425D6-127C-494B-93E7-B99DD22D3992}">
-  <dimension ref="A1:G18"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
-  <cols>
-    <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="13.5546875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" s="22" t="s">
-        <v>4051</v>
-      </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" t="s">
-        <v>4043</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4046</v>
-      </c>
-      <c r="C2" t="s">
-        <v>4044</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4045</v>
-      </c>
-      <c r="E2" s="20" t="s">
-        <v>4049</v>
-      </c>
-      <c r="F2" s="20" t="s">
-        <v>4052</v>
-      </c>
-      <c r="G2" s="20" t="s">
-        <v>4053</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>8</v>
-      </c>
-      <c r="C3" s="21">
-        <f>_xlfn.XLOOKUP(B3, 'XL STRINGS'!A:A, 'XL STRINGS'!E:E, "Not Found")</f>
-        <v>0</v>
-      </c>
-      <c r="D3" s="24">
-        <f>SUM(C3:C10)</f>
-        <v>12.347999999999999</v>
-      </c>
-      <c r="E3" s="25">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="F3" s="24">
-        <f>D3*E3</f>
-        <v>27.165600000000001</v>
-      </c>
-      <c r="G3" s="24">
-        <f>F3-D3</f>
-        <v>14.817600000000002</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>7</v>
-      </c>
-      <c r="B4" t="s">
-        <v>1982</v>
-      </c>
-      <c r="C4" s="21">
-        <f>_xlfn.XLOOKUP(B4, 'XL STRINGS'!A:A, 'XL STRINGS'!E:E, "Not Found")</f>
-        <v>3.6505000000000001</v>
-      </c>
-      <c r="D4" s="24"/>
-      <c r="E4" s="25"/>
-      <c r="F4" s="24"/>
-      <c r="G4" s="24"/>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>6</v>
-      </c>
-      <c r="B5" t="s">
-        <v>1949</v>
-      </c>
-      <c r="C5" s="21">
-        <f>_xlfn.XLOOKUP(B5, 'XL STRINGS'!A:A, 'XL STRINGS'!E:E, "Not Found")</f>
-        <v>2.3519999999999999</v>
-      </c>
-      <c r="D5" s="24"/>
-      <c r="E5" s="25"/>
-      <c r="F5" s="24"/>
-      <c r="G5" s="24"/>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>1937</v>
-      </c>
-      <c r="C6" s="21">
-        <f>_xlfn.XLOOKUP(B6, 'XL STRINGS'!A:A, 'XL STRINGS'!E:E, "Not Found")</f>
-        <v>2.0089999999999999</v>
-      </c>
-      <c r="D6" s="24"/>
-      <c r="E6" s="25"/>
-      <c r="F6" s="24"/>
-      <c r="G6" s="24"/>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>4</v>
-      </c>
-      <c r="B7" t="s">
-        <v>1916</v>
-      </c>
-      <c r="C7" s="21">
-        <f>_xlfn.XLOOKUP(B7, 'XL STRINGS'!A:A, 'XL STRINGS'!E:E, "Not Found")</f>
-        <v>1.7395</v>
-      </c>
-      <c r="D7" s="24"/>
-      <c r="E7" s="25"/>
-      <c r="F7" s="24"/>
-      <c r="G7" s="24"/>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>3</v>
-      </c>
-      <c r="B8" t="s">
-        <v>2792</v>
-      </c>
-      <c r="C8" s="21">
-        <f>_xlfn.XLOOKUP(B8, 'XL STRINGS'!A:A, 'XL STRINGS'!E:E, "Not Found")</f>
-        <v>0.88200000000000001</v>
-      </c>
-      <c r="D8" s="24"/>
-      <c r="E8" s="25"/>
-      <c r="F8" s="24"/>
-      <c r="G8" s="24"/>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>2</v>
-      </c>
-      <c r="B9" t="s">
-        <v>2771</v>
-      </c>
-      <c r="C9" s="21">
-        <f>_xlfn.XLOOKUP(B9, 'XL STRINGS'!A:A, 'XL STRINGS'!E:E, "Not Found")</f>
-        <v>0.85750000000000004</v>
-      </c>
-      <c r="D9" s="24"/>
-      <c r="E9" s="25"/>
-      <c r="F9" s="24"/>
-      <c r="G9" s="24"/>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>1</v>
-      </c>
-      <c r="B10" t="s">
-        <v>2723</v>
-      </c>
-      <c r="C10" s="21">
-        <f>_xlfn.XLOOKUP(B10, 'XL STRINGS'!A:A, 'XL STRINGS'!E:E, "Not Found")</f>
-        <v>0.85750000000000004</v>
-      </c>
-      <c r="D10" s="24"/>
-      <c r="E10" s="25"/>
-      <c r="F10" s="24"/>
-      <c r="G10" s="24"/>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="23" t="s">
-        <v>4050</v>
-      </c>
-      <c r="B12" s="23"/>
-      <c r="C12" s="23"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="23"/>
-      <c r="G12" s="23"/>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" t="s">
-        <v>4043</v>
-      </c>
-      <c r="B13" t="s">
-        <v>4046</v>
-      </c>
-      <c r="C13" t="s">
-        <v>4044</v>
-      </c>
-      <c r="D13" t="s">
-        <v>4045</v>
-      </c>
-      <c r="E13" s="20" t="s">
-        <v>4049</v>
-      </c>
-      <c r="F13" s="20" t="s">
-        <v>4052</v>
-      </c>
-      <c r="G13" s="20" t="s">
-        <v>4053</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>5</v>
-      </c>
-      <c r="B14" t="s">
-        <v>3392</v>
-      </c>
-      <c r="C14" s="21">
-        <f>_xlfn.XLOOKUP(B14, 'XLB Bass'!A:A, 'XLB Bass'!F:F, "Not Found")</f>
-        <v>10.682</v>
-      </c>
-      <c r="D14" s="24">
-        <f>SUM(C15:C18)</f>
-        <v>23.348500000000001</v>
-      </c>
-      <c r="E14" s="25">
-        <v>1.5</v>
-      </c>
-      <c r="F14" s="24">
-        <f>D14*E14</f>
-        <v>35.022750000000002</v>
-      </c>
-      <c r="G14" s="24">
-        <f>F14-D14</f>
-        <v>11.674250000000001</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>4</v>
-      </c>
-      <c r="B15" t="s">
-        <v>3353</v>
-      </c>
-      <c r="C15" s="21">
-        <f>_xlfn.XLOOKUP(B15, 'XLB Bass'!A:A, 'XLB Bass'!F:F, "Not Found")</f>
-        <v>7.1784999999999997</v>
-      </c>
-      <c r="D15" s="24"/>
-      <c r="E15" s="25"/>
-      <c r="F15" s="24"/>
-      <c r="G15" s="24"/>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>3</v>
-      </c>
-      <c r="B16" t="s">
-        <v>3332</v>
-      </c>
-      <c r="C16" s="21">
-        <f>_xlfn.XLOOKUP(B16, 'XLB Bass'!A:A, 'XLB Bass'!F:F, "Not Found")</f>
-        <v>5.9535</v>
-      </c>
-      <c r="D16" s="24"/>
-      <c r="E16" s="25"/>
-      <c r="F16" s="24"/>
-      <c r="G16" s="24"/>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>2</v>
-      </c>
-      <c r="B17" t="s">
-        <v>3317</v>
-      </c>
-      <c r="C17" s="21">
-        <f>_xlfn.XLOOKUP(B17, 'XLB Bass'!A:A, 'XLB Bass'!F:F, "Not Found")</f>
-        <v>5.5860000000000003</v>
-      </c>
-      <c r="D17" s="24"/>
-      <c r="E17" s="25"/>
-      <c r="F17" s="24"/>
-      <c r="G17" s="24"/>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>1</v>
-      </c>
-      <c r="B18" t="s">
-        <v>3305</v>
-      </c>
-      <c r="C18" s="21">
-        <f>_xlfn.XLOOKUP(B18, 'XLB Bass'!A:A, 'XLB Bass'!F:F, "Not Found")</f>
-        <v>4.6304999999999996</v>
-      </c>
-      <c r="D18" s="24"/>
-      <c r="E18" s="25"/>
-      <c r="F18" s="24"/>
-      <c r="G18" s="24"/>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="G14:G18"/>
-    <mergeCell ref="F14:F18"/>
-    <mergeCell ref="E14:E18"/>
-    <mergeCell ref="D14:D18"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="F3:F10"/>
-    <mergeCell ref="G3:G10"/>
-    <mergeCell ref="D3:D10"/>
-    <mergeCell ref="E3:E10"/>
-  </mergeCells>
-  <phoneticPr fontId="7" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{FCD577F8-E895-4AA4-AF80-052E555061C7}">
-          <x14:formula1>
-            <xm:f>'XL STRINGS'!$A$2:$A$62</xm:f>
-          </x14:formula1>
-          <xm:sqref>B3:B10</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{9B7FCD70-E802-4173-8580-369261AD873B}">
-          <x14:formula1>
-            <xm:f>'XLB Bass'!$A$1:$A$40</xm:f>
-          </x14:formula1>
-          <xm:sqref>B14:B18</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EB20580-F117-4EE2-9B90-DE496952B4D3}">
-  <dimension ref="A1:E62"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
-  <cols>
-    <col min="2" max="2" width="34.109375" customWidth="1"/>
-    <col min="3" max="3" width="21" customWidth="1"/>
-    <col min="4" max="4" width="18.33203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" t="s">
-        <v>4047</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4048</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="1" t="s">
-        <v>2714</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>2715</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>2716</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="2">
-        <v>0.85750000000000004</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="1" t="s">
-        <v>2717</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>2718</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>2719</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="2">
-        <v>0.85750000000000004</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="1" t="s">
-        <v>2720</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>2721</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>2722</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="2">
-        <v>0.85750000000000004</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="1" t="s">
-        <v>2723</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>2724</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>2725</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="2">
-        <v>0.85750000000000004</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="1" t="s">
-        <v>2726</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>2727</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>2728</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="2">
-        <v>0.85750000000000004</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="1" t="s">
-        <v>2732</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>2733</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>2734</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="2">
-        <v>0.85750000000000004</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="1" t="s">
-        <v>2735</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>2736</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>2737</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="2">
-        <v>0.85750000000000004</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="1" t="s">
-        <v>2741</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>2742</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>2743</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="2">
-        <v>0.85750000000000004</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="1" t="s">
-        <v>2744</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>2745</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>2746</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="2">
-        <v>0.85750000000000004</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="1" t="s">
-        <v>2750</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>2751</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>2752</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" s="2">
-        <v>0.85750000000000004</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="1" t="s">
-        <v>2753</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>2754</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>2755</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" s="2">
-        <v>0.85750000000000004</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="1" t="s">
-        <v>2759</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>2760</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>2761</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13" s="2">
-        <v>0.85750000000000004</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="1" t="s">
-        <v>2762</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>2763</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>2764</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E14" s="2">
-        <v>0.85750000000000004</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="1" t="s">
-        <v>2768</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>2769</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>2770</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E15" s="2">
-        <v>0.85750000000000004</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="1" t="s">
-        <v>2771</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>2772</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>2773</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E16" s="2">
-        <v>0.85750000000000004</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="1" t="s">
-        <v>2774</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>2775</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>2776</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E17" s="2">
-        <v>0.85750000000000004</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="1" t="s">
-        <v>2777</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>2778</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>2779</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E18" s="2">
-        <v>0.85750000000000004</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="1" t="s">
-        <v>2780</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>2781</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>2782</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E19" s="2">
-        <v>0.85750000000000004</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="1" t="s">
-        <v>2783</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>2784</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>2785</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E20" s="2">
-        <v>0.85750000000000004</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="1" t="s">
-        <v>2786</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>2787</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>2788</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E21" s="2">
-        <v>0.88200000000000001</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="1" t="s">
-        <v>2789</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>2790</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>2791</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E22" s="2">
-        <v>0.88200000000000001</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="1" t="s">
-        <v>2792</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>2793</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>2794</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E23" s="2">
-        <v>0.88200000000000001</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="1" t="s">
-        <v>2795</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>2796</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>2797</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E24" s="2">
-        <v>0.88200000000000001</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="1" t="s">
-        <v>2798</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>2799</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>2800</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E25" s="2">
-        <v>0.88200000000000001</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="1" t="s">
-        <v>1877</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>1878</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>1879</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E26" s="2">
-        <v>1.6415</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="1" t="s">
-        <v>1880</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>1881</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>1882</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E27" s="2">
-        <v>1.6415</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="1" t="s">
-        <v>1883</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>1884</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>1885</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E28" s="2">
-        <v>1.6415</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="1" t="s">
-        <v>1886</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>1887</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>1888</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E29" s="2">
-        <v>1.6415</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="1" t="s">
-        <v>1889</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>1890</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>1891</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E30" s="2">
-        <v>1.6415</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="1" t="s">
-        <v>1892</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>1893</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>1894</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E31" s="2">
-        <v>1.6415</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="1" t="s">
-        <v>1895</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>1896</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>1897</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E32" s="2">
-        <v>1.6415</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="1" t="s">
-        <v>1898</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>1899</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>1900</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E33" s="2">
-        <v>1.6415</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="1" t="s">
-        <v>1901</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>1902</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>1903</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E34" s="2">
-        <v>1.6415</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="1" t="s">
-        <v>1904</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>1905</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>1906</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E35" s="2">
-        <v>1.7395</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="1" t="s">
-        <v>1907</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>1908</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>1909</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E36" s="2">
-        <v>1.7395</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="1" t="s">
-        <v>1910</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>1911</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>1912</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E37" s="2">
-        <v>1.7395</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="1" t="s">
-        <v>1913</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>1914</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>1915</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E38" s="2">
-        <v>1.7395</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="1" t="s">
-        <v>1916</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>1917</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>1918</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E39" s="2">
-        <v>1.7395</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="1" t="s">
-        <v>1919</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>1920</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>1921</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E40" s="2">
-        <v>2.0089999999999999</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="1" t="s">
-        <v>1922</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>1923</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>1924</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E41" s="2">
-        <v>2.0089999999999999</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="1" t="s">
-        <v>1925</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>1926</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>1927</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E42" s="2">
-        <v>2.0089999999999999</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="1" t="s">
-        <v>1928</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>1929</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>1930</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E43" s="2">
-        <v>2.0089999999999999</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="1" t="s">
-        <v>1931</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>1932</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>1933</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E44" s="2">
-        <v>2.0089999999999999</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="1" t="s">
-        <v>1934</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>1935</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>1936</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E45" s="2">
-        <v>2.0089999999999999</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="1" t="s">
-        <v>1937</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>1938</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>1939</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E46" s="2">
-        <v>2.0089999999999999</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="1" t="s">
-        <v>1940</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>1941</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>1942</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E47" s="2">
-        <v>2.0089999999999999</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="1" t="s">
-        <v>1943</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>1944</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>1945</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E48" s="2">
-        <v>2.0089999999999999</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="1" t="s">
-        <v>1946</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>1947</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>1948</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E49" s="2">
-        <v>2.0089999999999999</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="1" t="s">
-        <v>1949</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>1950</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>1951</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E50" s="2">
-        <v>2.3519999999999999</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="1" t="s">
-        <v>1952</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>1953</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>1954</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E51" s="2">
-        <v>2.3519999999999999</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="1" t="s">
-        <v>1955</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>1956</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>1957</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E52" s="2">
-        <v>2.3519999999999999</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="1" t="s">
-        <v>1958</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>1959</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>1960</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E53" s="2">
-        <v>2.3519999999999999</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="1" t="s">
-        <v>1961</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>1962</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>1963</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E54" s="2">
-        <v>2.3519999999999999</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="1" t="s">
-        <v>1964</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>1965</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>1966</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E55" s="2">
-        <v>2.94</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="1" t="s">
-        <v>1967</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>1968</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>1969</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E56" s="2">
-        <v>2.94</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="1" t="s">
-        <v>1970</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>1971</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>1972</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E57" s="2">
-        <v>2.94</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="1" t="s">
-        <v>1973</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>1974</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>1975</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E58" s="2">
-        <v>3.6505000000000001</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="1" t="s">
-        <v>1976</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>1977</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>1978</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E59" s="2">
-        <v>3.6505000000000001</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="1" t="s">
-        <v>1979</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>1980</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>1981</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E60" s="2">
-        <v>3.6505000000000001</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="1" t="s">
-        <v>1982</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>1983</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>1984</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E61" s="2">
-        <v>3.6505000000000001</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="1" t="s">
-        <v>1985</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>1986</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>1987</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E62" s="2">
-        <v>4.9000000000000004</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93192DFF-B180-49A7-B8B4-95F52EBB6A9D}">
-  <dimension ref="A1:F40"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
-  <cols>
-    <col min="2" max="2" width="32.21875" customWidth="1"/>
-    <col min="3" max="3" width="17.6640625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="5" t="s">
-        <v>3281</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>3282</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>3283</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E1" s="6">
-        <v>5.8</v>
-      </c>
-      <c r="F1" s="6">
-        <v>2.8420000000000001</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="5" t="s">
-        <v>3284</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>3285</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>3286</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="6">
-        <v>7.65</v>
-      </c>
-      <c r="F2" s="6">
-        <v>3.7484999999999999</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="5" t="s">
-        <v>3287</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>3288</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>3289</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="6">
-        <v>8.4</v>
-      </c>
-      <c r="F3" s="6">
-        <v>4.1159999999999997</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="5" t="s">
-        <v>3290</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>3291</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>3292</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="6">
-        <v>8.4</v>
-      </c>
-      <c r="F4" s="6">
-        <v>4.1159999999999997</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="5" t="s">
-        <v>3293</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>3294</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>3295</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="6">
-        <v>9.4499999999999993</v>
-      </c>
-      <c r="F5" s="6">
-        <v>4.6304999999999996</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="5" t="s">
-        <v>3296</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>3297</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>3298</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="6">
-        <v>9.4499999999999993</v>
-      </c>
-      <c r="F6" s="6">
-        <v>4.6304999999999996</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
-        <v>3299</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>3300</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>3301</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="6">
-        <v>9.4499999999999993</v>
-      </c>
-      <c r="F7" s="6">
-        <v>4.6304999999999996</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
-        <v>3302</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>3303</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>3304</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="6">
-        <v>9.4499999999999993</v>
-      </c>
-      <c r="F8" s="6">
-        <v>4.6304999999999996</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
-        <v>3305</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>3306</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>3307</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="6">
-        <v>9.4499999999999993</v>
-      </c>
-      <c r="F9" s="6">
-        <v>4.6304999999999996</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
-        <v>3308</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>3309</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>3310</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="6">
-        <v>9.4499999999999993</v>
-      </c>
-      <c r="F10" s="6">
-        <v>4.6304999999999996</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
-        <v>3311</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>3312</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>3313</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" s="6">
-        <v>9.4499999999999993</v>
-      </c>
-      <c r="F11" s="6">
-        <v>4.6304999999999996</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
-        <v>3314</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>3315</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>3316</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" s="6">
-        <v>9.4499999999999993</v>
-      </c>
-      <c r="F12" s="6">
-        <v>4.6304999999999996</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
-        <v>3317</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>3318</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>3319</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13" s="6">
-        <v>11.4</v>
-      </c>
-      <c r="F13" s="6">
-        <v>5.5860000000000003</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
-        <v>3320</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>3321</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>3322</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E14" s="6">
-        <v>11.4</v>
-      </c>
-      <c r="F14" s="6">
-        <v>5.5860000000000003</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
-        <v>3323</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>3324</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>3325</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E15" s="6">
-        <v>11.4</v>
-      </c>
-      <c r="F15" s="6">
-        <v>5.5860000000000003</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
-        <v>3326</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>3327</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>3328</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E16" s="6">
-        <v>11.4</v>
-      </c>
-      <c r="F16" s="6">
-        <v>5.5860000000000003</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="5" t="s">
-        <v>3329</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>3330</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>3331</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E17" s="6">
-        <v>12.15</v>
-      </c>
-      <c r="F17" s="6">
-        <v>5.9535</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="5" t="s">
-        <v>3332</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>3333</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>3334</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E18" s="6">
-        <v>12.15</v>
-      </c>
-      <c r="F18" s="6">
-        <v>5.9535</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19" s="5" t="s">
-        <v>3335</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>3336</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>3337</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E19" s="6">
-        <v>12.15</v>
-      </c>
-      <c r="F19" s="6">
-        <v>5.9535</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20" s="5" t="s">
-        <v>3338</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>3339</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>3340</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E20" s="6">
-        <v>14.65</v>
-      </c>
-      <c r="F20" s="6">
-        <v>7.1784999999999997</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21" s="5" t="s">
-        <v>3341</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>3342</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>3343</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E21" s="6">
-        <v>14.65</v>
-      </c>
-      <c r="F21" s="6">
-        <v>7.1784999999999997</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22" s="5" t="s">
-        <v>3344</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>3345</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>3346</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E22" s="6">
-        <v>14.65</v>
-      </c>
-      <c r="F22" s="6">
-        <v>7.1784999999999997</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23" s="5" t="s">
-        <v>3347</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>3348</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>3349</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E23" s="6">
-        <v>14.65</v>
-      </c>
-      <c r="F23" s="6">
-        <v>7.1784999999999997</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24" s="5" t="s">
-        <v>3350</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>3351</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>3352</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E24" s="6">
-        <v>14.65</v>
-      </c>
-      <c r="F24" s="6">
-        <v>7.1784999999999997</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25" s="5" t="s">
-        <v>3353</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>3354</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>3355</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E25" s="6">
-        <v>14.65</v>
-      </c>
-      <c r="F25" s="6">
-        <v>7.1784999999999997</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26" s="5" t="s">
-        <v>3356</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>3357</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>3358</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E26" s="6">
-        <v>16.3</v>
-      </c>
-      <c r="F26" s="6">
-        <v>7.9870000000000001</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27" s="5" t="s">
-        <v>3359</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>3360</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>3361</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E27" s="6">
-        <v>19.3</v>
-      </c>
-      <c r="F27" s="6">
-        <v>9.4570000000000007</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28" s="5" t="s">
-        <v>3362</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>3363</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>3364</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E28" s="6">
-        <v>16.3</v>
-      </c>
-      <c r="F28" s="6">
-        <v>7.9870000000000001</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29" s="5" t="s">
-        <v>3365</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>3366</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>3367</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E29" s="6">
-        <v>19.3</v>
-      </c>
-      <c r="F29" s="6">
-        <v>9.4570000000000007</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30" s="5" t="s">
-        <v>3368</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>3369</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>3370</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E30" s="6">
-        <v>16.3</v>
-      </c>
-      <c r="F30" s="6">
-        <v>7.9870000000000001</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31" s="5" t="s">
-        <v>3371</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>3372</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>3373</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E31" s="6">
-        <v>16.3</v>
-      </c>
-      <c r="F31" s="6">
-        <v>7.9870000000000001</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32" s="5" t="s">
-        <v>3374</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>3375</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>3376</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E32" s="6">
-        <v>19.3</v>
-      </c>
-      <c r="F32" s="6">
-        <v>9.4570000000000007</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33" s="5" t="s">
-        <v>3377</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>3378</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>3379</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E33" s="6">
-        <v>16.3</v>
-      </c>
-      <c r="F33" s="6">
-        <v>7.9870000000000001</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34" s="5" t="s">
-        <v>3380</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>3381</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>3382</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E34" s="6">
-        <v>19.3</v>
-      </c>
-      <c r="F34" s="6">
-        <v>9.4570000000000007</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35" s="5" t="s">
-        <v>3383</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>3384</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>3385</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E35" s="6">
-        <v>16.3</v>
-      </c>
-      <c r="F35" s="6">
-        <v>7.9870000000000001</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36" s="5" t="s">
-        <v>3386</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>3387</v>
-      </c>
-      <c r="C36" s="5" t="s">
-        <v>3388</v>
-      </c>
-      <c r="D36" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E36" s="6">
-        <v>20.3</v>
-      </c>
-      <c r="F36" s="6">
-        <v>9.9469999999999992</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37" s="5" t="s">
-        <v>3389</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>3390</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>3391</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E37" s="6">
-        <v>18.850000000000001</v>
-      </c>
-      <c r="F37" s="6">
-        <v>9.2364999999999995</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38" s="5" t="s">
-        <v>3392</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>3393</v>
-      </c>
-      <c r="C38" s="5" t="s">
-        <v>3394</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E38" s="6">
-        <v>21.8</v>
-      </c>
-      <c r="F38" s="6">
-        <v>10.682</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39" s="5" t="s">
-        <v>3395</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>3396</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>3397</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E39" s="6">
-        <v>24.6</v>
-      </c>
-      <c r="F39" s="6">
-        <v>12.054</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40" s="5" t="s">
-        <v>3398</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>3399</v>
-      </c>
-      <c r="C40" s="5" t="s">
-        <v>3400</v>
-      </c>
-      <c r="D40" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E40" s="6">
-        <v>27</v>
-      </c>
-      <c r="F40" s="6">
-        <v>13.23</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K1348"/>
-  <sheetFormatPr defaultColWidth="22" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="22" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16" style="1" customWidth="1"/>
     <col min="2" max="2" width="36" style="1" customWidth="1"/>
     <col min="3" max="3" width="22" style="1"/>
     <col min="4" max="4" width="20" style="1" customWidth="1"/>
-    <col min="5" max="5" width="12.5546875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="14.109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="12.5703125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="14.140625" style="1" customWidth="1"/>
     <col min="7" max="16384" width="22" style="1"/>
   </cols>
   <sheetData>
@@ -28093,7 +25792,7 @@
       </c>
       <c r="I624" s="2"/>
     </row>
-    <row r="625" spans="1:11" ht="15" thickBot="1">
+    <row r="625" spans="1:11" ht="15.75" thickBot="1">
       <c r="A625" s="1" t="s">
         <v>1874</v>
       </c>
@@ -28114,7 +25813,7 @@
       </c>
       <c r="I625" s="2"/>
     </row>
-    <row r="626" spans="1:11" ht="16.2" thickBot="1">
+    <row r="626" spans="1:11" ht="16.5" thickBot="1">
       <c r="A626" s="1" t="s">
         <v>1877</v>
       </c>
@@ -28147,7 +25846,7 @@
         <v>3.44</v>
       </c>
     </row>
-    <row r="627" spans="1:11" ht="16.2" thickBot="1">
+    <row r="627" spans="1:11" ht="16.5" thickBot="1">
       <c r="A627" s="1" t="s">
         <v>1880</v>
       </c>
@@ -28180,7 +25879,7 @@
         <v>3.44</v>
       </c>
     </row>
-    <row r="628" spans="1:11" ht="16.2" thickBot="1">
+    <row r="628" spans="1:11" ht="16.5" thickBot="1">
       <c r="A628" s="1" t="s">
         <v>1883</v>
       </c>
@@ -28213,7 +25912,7 @@
         <v>3.44</v>
       </c>
     </row>
-    <row r="629" spans="1:11" ht="16.2" thickBot="1">
+    <row r="629" spans="1:11" ht="16.5" thickBot="1">
       <c r="A629" s="1" t="s">
         <v>1886</v>
       </c>
@@ -28246,7 +25945,7 @@
         <v>3.44</v>
       </c>
     </row>
-    <row r="630" spans="1:11" ht="16.2" thickBot="1">
+    <row r="630" spans="1:11" ht="16.5" thickBot="1">
       <c r="A630" s="1" t="s">
         <v>1889</v>
       </c>
@@ -28279,7 +25978,7 @@
         <v>6.88</v>
       </c>
     </row>
-    <row r="631" spans="1:11" ht="16.2" thickBot="1">
+    <row r="631" spans="1:11" ht="16.5" thickBot="1">
       <c r="A631" s="1" t="s">
         <v>1892</v>
       </c>
@@ -28312,7 +26011,7 @@
         <v>3.44</v>
       </c>
     </row>
-    <row r="632" spans="1:11" ht="16.2" thickBot="1">
+    <row r="632" spans="1:11" ht="16.5" thickBot="1">
       <c r="A632" s="1" t="s">
         <v>1895</v>
       </c>
@@ -28345,7 +26044,7 @@
         <v>3.44</v>
       </c>
     </row>
-    <row r="633" spans="1:11" ht="16.2" thickBot="1">
+    <row r="633" spans="1:11" ht="16.5" thickBot="1">
       <c r="A633" s="1" t="s">
         <v>1898</v>
       </c>
@@ -28378,7 +26077,7 @@
         <v>6.88</v>
       </c>
     </row>
-    <row r="634" spans="1:11" ht="16.2" thickBot="1">
+    <row r="634" spans="1:11" ht="16.5" thickBot="1">
       <c r="A634" s="1" t="s">
         <v>1901</v>
       </c>
@@ -28411,7 +26110,7 @@
         <v>7.04</v>
       </c>
     </row>
-    <row r="635" spans="1:11" ht="16.2" thickBot="1">
+    <row r="635" spans="1:11" ht="16.5" thickBot="1">
       <c r="A635" s="1" t="s">
         <v>1904</v>
       </c>
@@ -28444,7 +26143,7 @@
         <v>13.12</v>
       </c>
     </row>
-    <row r="636" spans="1:11" ht="16.2" thickBot="1">
+    <row r="636" spans="1:11" ht="16.5" thickBot="1">
       <c r="A636" s="1" t="s">
         <v>1907</v>
       </c>
@@ -28477,7 +26176,7 @@
         <v>13.92</v>
       </c>
     </row>
-    <row r="637" spans="1:11" ht="16.2" thickBot="1">
+    <row r="637" spans="1:11" ht="16.5" thickBot="1">
       <c r="A637" s="1" t="s">
         <v>1910</v>
       </c>
@@ -28510,7 +26209,7 @@
         <v>6.96</v>
       </c>
     </row>
-    <row r="638" spans="1:11" ht="16.2" thickBot="1">
+    <row r="638" spans="1:11" ht="16.5" thickBot="1">
       <c r="A638" s="1" t="s">
         <v>1913</v>
       </c>
@@ -28543,7 +26242,7 @@
         <v>8.0399999999999991</v>
       </c>
     </row>
-    <row r="639" spans="1:11" ht="16.2" thickBot="1">
+    <row r="639" spans="1:11" ht="16.5" thickBot="1">
       <c r="A639" s="1" t="s">
         <v>1916</v>
       </c>
@@ -28576,7 +26275,7 @@
         <v>16.079999999999998</v>
       </c>
     </row>
-    <row r="640" spans="1:11" ht="16.2" thickBot="1">
+    <row r="640" spans="1:11" ht="16.5" thickBot="1">
       <c r="A640" s="1" t="s">
         <v>1919</v>
       </c>
@@ -28609,7 +26308,7 @@
         <v>8.0399999999999991</v>
       </c>
     </row>
-    <row r="641" spans="1:11" ht="16.2" thickBot="1">
+    <row r="641" spans="1:11" ht="16.5" thickBot="1">
       <c r="A641" s="1" t="s">
         <v>1922</v>
       </c>
@@ -28642,7 +26341,7 @@
         <v>18.8</v>
       </c>
     </row>
-    <row r="642" spans="1:11" ht="16.2" thickBot="1">
+    <row r="642" spans="1:11" ht="16.5" thickBot="1">
       <c r="A642" s="1" t="s">
         <v>1925</v>
       </c>
@@ -43515,26 +41214,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8ef722f7-2903-4cc3-bd62-aaec75d433d8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="65106227-dbb6-4320-ac11-00ba931273f5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100DB658CC6197FFF408FDABED29385577E" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="26104523e1eb7428da8f0121e18b0a52">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8ef722f7-2903-4cc3-bd62-aaec75d433d8" xmlns:ns3="65106227-dbb6-4320-ac11-00ba931273f5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ecd17e0f0f17b24061d1705f9eed6a8b" ns2:_="" ns3:_="">
     <xsd:import namespace="8ef722f7-2903-4cc3-bd62-aaec75d433d8"/>
@@ -43735,10 +41414,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8ef722f7-2903-4cc3-bd62-aaec75d433d8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="65106227-dbb6-4320-ac11-00ba931273f5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{84F40B6C-ED3D-4837-B32D-DFBD21D8EF85}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4C34FC29-4807-409A-88C0-7A43EF2D4ACF}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="8ef722f7-2903-4cc3-bd62-aaec75d433d8"/>
+    <ds:schemaRef ds:uri="65106227-dbb6-4320-ac11-00ba931273f5"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -43755,5 +41465,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4C34FC29-4807-409A-88C0-7A43EF2D4ACF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{84F40B6C-ED3D-4837-B32D-DFBD21D8EF85}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>